--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128913020</v>
+        <v>128913037</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503230</v>
+        <v>503310</v>
       </c>
       <c r="R3" t="n">
-        <v>7023714</v>
+        <v>7023572</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128913037</v>
+        <v>128913020</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503310</v>
+        <v>503230</v>
       </c>
       <c r="R4" t="n">
-        <v>7023572</v>
+        <v>7023714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128913036</v>
+        <v>128913015</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>88768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503322</v>
+        <v>503283</v>
       </c>
       <c r="R5" t="n">
-        <v>7023622</v>
+        <v>7023665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128913015</v>
+        <v>128913036</v>
       </c>
       <c r="B6" t="n">
-        <v>88768</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503283</v>
+        <v>503322</v>
       </c>
       <c r="R6" t="n">
-        <v>7023665</v>
+        <v>7023622</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2686,10 +2686,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128913018</v>
+        <v>128913014</v>
       </c>
       <c r="B22" t="n">
-        <v>57716</v>
+        <v>88768</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503223</v>
+        <v>503302</v>
       </c>
       <c r="R22" t="n">
-        <v>7023673</v>
+        <v>7023681</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2757,11 +2757,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2788,10 +2783,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128913014</v>
+        <v>128913018</v>
       </c>
       <c r="B23" t="n">
-        <v>88768</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2799,21 +2794,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2823,10 +2818,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503302</v>
+        <v>503223</v>
       </c>
       <c r="R23" t="n">
-        <v>7023681</v>
+        <v>7023673</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,6 +2854,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128913038</v>
       </c>
       <c r="B2" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128913037</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128913020</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128913015</v>
+        <v>128913036</v>
       </c>
       <c r="B5" t="n">
-        <v>88768</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503283</v>
+        <v>503322</v>
       </c>
       <c r="R5" t="n">
-        <v>7023665</v>
+        <v>7023622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128913036</v>
+        <v>128913015</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>88772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503322</v>
+        <v>503283</v>
       </c>
       <c r="R6" t="n">
-        <v>7023622</v>
+        <v>7023665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128913032</v>
+        <v>128913021</v>
       </c>
       <c r="B7" t="n">
-        <v>57876</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,50 +1176,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503298</v>
+        <v>503250</v>
       </c>
       <c r="R7" t="n">
-        <v>7023667</v>
+        <v>7023749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1278,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128913021</v>
+        <v>128913032</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>57880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,34 +1278,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503250</v>
+        <v>503298</v>
       </c>
       <c r="R8" t="n">
-        <v>7023749</v>
+        <v>7023667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1349,11 +1354,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1383,7 +1383,7 @@
         <v>128913013</v>
       </c>
       <c r="B9" t="n">
-        <v>88768</v>
+        <v>88772</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>128913023</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>128913030</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>128913022</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>128913028</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128913033</v>
       </c>
       <c r="B14" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>128913035</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>128913024</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128913019</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>128913017</v>
       </c>
       <c r="B18" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>128913029</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>128913026</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>128913025</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>128913014</v>
       </c>
       <c r="B22" t="n">
-        <v>88768</v>
+        <v>88772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>128913018</v>
       </c>
       <c r="B23" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128913036</v>
+        <v>128913015</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>88772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503322</v>
+        <v>503283</v>
       </c>
       <c r="R5" t="n">
-        <v>7023622</v>
+        <v>7023665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128913015</v>
+        <v>128913036</v>
       </c>
       <c r="B6" t="n">
-        <v>88772</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503283</v>
+        <v>503322</v>
       </c>
       <c r="R6" t="n">
-        <v>7023665</v>
+        <v>7023622</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128913037</v>
+        <v>128913020</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503310</v>
+        <v>503230</v>
       </c>
       <c r="R3" t="n">
-        <v>7023572</v>
+        <v>7023714</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128913020</v>
+        <v>128913037</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503230</v>
+        <v>503310</v>
       </c>
       <c r="R4" t="n">
-        <v>7023714</v>
+        <v>7023572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128913015</v>
+        <v>128913036</v>
       </c>
       <c r="B5" t="n">
-        <v>88772</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503283</v>
+        <v>503322</v>
       </c>
       <c r="R5" t="n">
-        <v>7023665</v>
+        <v>7023622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128913036</v>
+        <v>128913015</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>88772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503322</v>
+        <v>503283</v>
       </c>
       <c r="R6" t="n">
-        <v>7023622</v>
+        <v>7023665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2686,10 +2686,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128913014</v>
+        <v>128913018</v>
       </c>
       <c r="B22" t="n">
-        <v>88772</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503302</v>
+        <v>503223</v>
       </c>
       <c r="R22" t="n">
-        <v>7023681</v>
+        <v>7023673</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2757,6 +2757,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2783,10 +2788,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128913018</v>
+        <v>128913014</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>88772</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2794,21 +2799,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2818,10 +2823,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503223</v>
+        <v>503302</v>
       </c>
       <c r="R23" t="n">
-        <v>7023673</v>
+        <v>7023681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,11 +2859,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128913038</v>
       </c>
       <c r="B2" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128913020</v>
+        <v>128913037</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503230</v>
+        <v>503310</v>
       </c>
       <c r="R3" t="n">
-        <v>7023714</v>
+        <v>7023572</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128913037</v>
+        <v>128913020</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503310</v>
+        <v>503230</v>
       </c>
       <c r="R4" t="n">
-        <v>7023572</v>
+        <v>7023714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128913036</v>
+        <v>128913015</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>88777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503322</v>
+        <v>503283</v>
       </c>
       <c r="R5" t="n">
-        <v>7023622</v>
+        <v>7023665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128913015</v>
+        <v>128913036</v>
       </c>
       <c r="B6" t="n">
-        <v>88772</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503283</v>
+        <v>503322</v>
       </c>
       <c r="R6" t="n">
-        <v>7023665</v>
+        <v>7023622</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
         <v>128913021</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128913032</v>
       </c>
       <c r="B8" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>128913013</v>
       </c>
       <c r="B9" t="n">
-        <v>88772</v>
+        <v>88777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>128913023</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>128913030</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>128913022</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>128913028</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128913033</v>
       </c>
       <c r="B14" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>128913035</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>128913024</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128913019</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>128913017</v>
       </c>
       <c r="B18" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>128913029</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>128913026</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>128913025</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>128913018</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>128913014</v>
       </c>
       <c r="B23" t="n">
-        <v>88772</v>
+        <v>88777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128913020</v>
+        <v>128913037</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503230</v>
+        <v>503310</v>
       </c>
       <c r="R3" t="n">
-        <v>7023714</v>
+        <v>7023572</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128913037</v>
+        <v>128913020</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503310</v>
+        <v>503230</v>
       </c>
       <c r="R4" t="n">
-        <v>7023572</v>
+        <v>7023714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,7 +974,7 @@
         <v>128913015</v>
       </c>
       <c r="B5" t="n">
-        <v>88784</v>
+        <v>88787</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>128913013</v>
       </c>
       <c r="B9" t="n">
-        <v>88784</v>
+        <v>88787</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128913033</v>
       </c>
       <c r="B14" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2686,10 +2686,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128913018</v>
+        <v>128913014</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>88787</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503223</v>
+        <v>503302</v>
       </c>
       <c r="R22" t="n">
-        <v>7023673</v>
+        <v>7023681</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2757,11 +2757,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2788,10 +2783,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128913014</v>
+        <v>128913018</v>
       </c>
       <c r="B23" t="n">
-        <v>88784</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2799,21 +2794,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2823,10 +2818,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503302</v>
+        <v>503223</v>
       </c>
       <c r="R23" t="n">
-        <v>7023681</v>
+        <v>7023673</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,6 +2854,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128913038</v>
       </c>
       <c r="B2" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128913037</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128913015</v>
       </c>
       <c r="B5" t="n">
-        <v>88787</v>
+        <v>88790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128913036</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>128913013</v>
       </c>
       <c r="B9" t="n">
-        <v>88787</v>
+        <v>88790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128913033</v>
       </c>
       <c r="B14" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>128913035</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>128913017</v>
       </c>
       <c r="B18" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,10 +2686,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128913014</v>
+        <v>128913018</v>
       </c>
       <c r="B22" t="n">
-        <v>88787</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503302</v>
+        <v>503223</v>
       </c>
       <c r="R22" t="n">
-        <v>7023681</v>
+        <v>7023673</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2757,6 +2757,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2783,10 +2788,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128913018</v>
+        <v>128913014</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>88790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2794,21 +2799,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2818,10 +2823,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503223</v>
+        <v>503302</v>
       </c>
       <c r="R23" t="n">
-        <v>7023673</v>
+        <v>7023681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,11 +2859,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128913021</v>
+        <v>128913032</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,34 +1176,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503250</v>
+        <v>503298</v>
       </c>
       <c r="R7" t="n">
-        <v>7023749</v>
+        <v>7023667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1252,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128913032</v>
+        <v>128913021</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,50 +1289,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503298</v>
+        <v>503250</v>
       </c>
       <c r="R8" t="n">
-        <v>7023667</v>
+        <v>7023749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,6 +1349,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128913032</v>
+        <v>128913021</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,50 +1176,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503298</v>
+        <v>503250</v>
       </c>
       <c r="R7" t="n">
-        <v>7023667</v>
+        <v>7023749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1278,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128913021</v>
+        <v>128913032</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,34 +1278,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503250</v>
+        <v>503298</v>
       </c>
       <c r="R8" t="n">
-        <v>7023749</v>
+        <v>7023667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1349,11 +1354,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2686,10 +2686,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128913018</v>
+        <v>128913014</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>88790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503223</v>
+        <v>503302</v>
       </c>
       <c r="R22" t="n">
-        <v>7023673</v>
+        <v>7023681</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2757,11 +2757,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2788,10 +2783,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128913014</v>
+        <v>128913018</v>
       </c>
       <c r="B23" t="n">
-        <v>88790</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2799,21 +2794,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2823,10 +2818,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503302</v>
+        <v>503223</v>
       </c>
       <c r="R23" t="n">
-        <v>7023681</v>
+        <v>7023673</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,6 +2854,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128913038</v>
       </c>
       <c r="B2" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128913037</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128913020</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128913015</v>
       </c>
       <c r="B5" t="n">
-        <v>88790</v>
+        <v>88794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128913036</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128913021</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128913032</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>128913013</v>
       </c>
       <c r="B9" t="n">
-        <v>88790</v>
+        <v>88794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>128913023</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>128913030</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>128913022</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>128913028</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128913033</v>
       </c>
       <c r="B14" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>128913035</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>128913024</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128913019</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>128913017</v>
       </c>
       <c r="B18" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>128913029</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>128913026</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>128913025</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>128913014</v>
       </c>
       <c r="B22" t="n">
-        <v>88790</v>
+        <v>88794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>128913018</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -2686,10 +2686,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128913014</v>
+        <v>128913018</v>
       </c>
       <c r="B22" t="n">
-        <v>88794</v>
+        <v>57725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503302</v>
+        <v>503223</v>
       </c>
       <c r="R22" t="n">
-        <v>7023681</v>
+        <v>7023673</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2757,6 +2757,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2783,10 +2788,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128913018</v>
+        <v>128913014</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>88794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2794,21 +2799,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2818,10 +2823,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503223</v>
+        <v>503302</v>
       </c>
       <c r="R23" t="n">
-        <v>7023673</v>
+        <v>7023681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,11 +2859,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128913038</v>
       </c>
       <c r="B2" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128913015</v>
+        <v>128913036</v>
       </c>
       <c r="B5" t="n">
-        <v>88794</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503283</v>
+        <v>503322</v>
       </c>
       <c r="R5" t="n">
-        <v>7023665</v>
+        <v>7023622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128913036</v>
+        <v>128913015</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>88801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503322</v>
+        <v>503283</v>
       </c>
       <c r="R6" t="n">
-        <v>7023622</v>
+        <v>7023665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1383,7 +1383,7 @@
         <v>128913013</v>
       </c>
       <c r="B9" t="n">
-        <v>88794</v>
+        <v>88801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128913033</v>
       </c>
       <c r="B14" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>128913017</v>
       </c>
       <c r="B18" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,10 +2686,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128913018</v>
+        <v>128913014</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>88801</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503223</v>
+        <v>503302</v>
       </c>
       <c r="R22" t="n">
-        <v>7023673</v>
+        <v>7023681</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2757,11 +2757,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2788,10 +2783,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128913014</v>
+        <v>128913018</v>
       </c>
       <c r="B23" t="n">
-        <v>88794</v>
+        <v>57725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2799,21 +2794,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2823,10 +2818,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503302</v>
+        <v>503223</v>
       </c>
       <c r="R23" t="n">
-        <v>7023681</v>
+        <v>7023673</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,6 +2854,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128913038</v>
       </c>
       <c r="B2" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128913037</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128913020</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128913036</v>
+        <v>128913015</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>88803</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503322</v>
+        <v>503283</v>
       </c>
       <c r="R5" t="n">
-        <v>7023622</v>
+        <v>7023665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128913015</v>
+        <v>128913036</v>
       </c>
       <c r="B6" t="n">
-        <v>88801</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503283</v>
+        <v>503322</v>
       </c>
       <c r="R6" t="n">
-        <v>7023665</v>
+        <v>7023622</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
         <v>128913021</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128913032</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>128913013</v>
       </c>
       <c r="B9" t="n">
-        <v>88801</v>
+        <v>88803</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>128913023</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>128913030</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>128913022</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>128913028</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128913033</v>
       </c>
       <c r="B14" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>128913035</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>128913024</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>128913019</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>128913017</v>
       </c>
       <c r="B18" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>128913029</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>128913026</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>128913025</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2686,10 +2686,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128913014</v>
+        <v>128913018</v>
       </c>
       <c r="B22" t="n">
-        <v>88801</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503302</v>
+        <v>503223</v>
       </c>
       <c r="R22" t="n">
-        <v>7023681</v>
+        <v>7023673</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2757,6 +2757,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2783,10 +2788,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128913018</v>
+        <v>128913014</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>88803</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2794,21 +2799,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2818,10 +2823,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503223</v>
+        <v>503302</v>
       </c>
       <c r="R23" t="n">
-        <v>7023673</v>
+        <v>7023681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,11 +2859,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128913021</v>
+        <v>128913032</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,34 +1176,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503250</v>
+        <v>503298</v>
       </c>
       <c r="R7" t="n">
-        <v>7023749</v>
+        <v>7023667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1252,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128913032</v>
+        <v>128913021</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,50 +1289,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503298</v>
+        <v>503250</v>
       </c>
       <c r="R8" t="n">
-        <v>7023667</v>
+        <v>7023749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,6 +1349,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2686,10 +2686,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128913018</v>
+        <v>128913014</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>88803</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503223</v>
+        <v>503302</v>
       </c>
       <c r="R22" t="n">
-        <v>7023673</v>
+        <v>7023681</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2757,11 +2757,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2788,10 +2783,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128913014</v>
+        <v>128913018</v>
       </c>
       <c r="B23" t="n">
-        <v>88803</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2799,21 +2794,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2823,10 +2818,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503302</v>
+        <v>503223</v>
       </c>
       <c r="R23" t="n">
-        <v>7023681</v>
+        <v>7023673</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,6 +2854,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128913015</v>
       </c>
       <c r="B5" t="n">
-        <v>88803</v>
+        <v>88804</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>128913013</v>
       </c>
       <c r="B9" t="n">
-        <v>88803</v>
+        <v>88804</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128913033</v>
       </c>
       <c r="B14" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>128913014</v>
       </c>
       <c r="B22" t="n">
-        <v>88803</v>
+        <v>88804</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128913032</v>
+        <v>128913021</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,50 +1176,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503298</v>
+        <v>503250</v>
       </c>
       <c r="R7" t="n">
-        <v>7023667</v>
+        <v>7023749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1278,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128913021</v>
+        <v>128913032</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,34 +1278,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503250</v>
+        <v>503298</v>
       </c>
       <c r="R8" t="n">
-        <v>7023749</v>
+        <v>7023667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1349,11 +1354,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128913037</v>
+        <v>128913020</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503310</v>
+        <v>503230</v>
       </c>
       <c r="R3" t="n">
-        <v>7023572</v>
+        <v>7023714</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,6 +845,11 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -857,22 +862,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128913020</v>
+        <v>128913037</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503230</v>
+        <v>503310</v>
       </c>
       <c r="R4" t="n">
-        <v>7023714</v>
+        <v>7023572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,11 +947,6 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -959,12 +959,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1056,12 +1056,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1153,12 +1153,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1255,12 +1255,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1368,12 +1368,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1465,12 +1465,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1567,12 +1567,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1669,12 +1669,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1771,12 +1771,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1873,12 +1873,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1970,12 +1970,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2067,12 +2067,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2169,12 +2169,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2271,12 +2271,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2368,12 +2368,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2470,12 +2470,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2572,12 +2572,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2674,12 +2674,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2771,12 +2771,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2873,12 +2873,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128913038</v>
       </c>
       <c r="B2" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128913037</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128913015</v>
+        <v>128913036</v>
       </c>
       <c r="B5" t="n">
-        <v>88804</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503283</v>
+        <v>503322</v>
       </c>
       <c r="R5" t="n">
-        <v>7023665</v>
+        <v>7023622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128913036</v>
+        <v>128913015</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>88807</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503322</v>
+        <v>503283</v>
       </c>
       <c r="R6" t="n">
-        <v>7023622</v>
+        <v>7023665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1383,7 +1383,7 @@
         <v>128913013</v>
       </c>
       <c r="B9" t="n">
-        <v>88804</v>
+        <v>88807</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128913033</v>
       </c>
       <c r="B14" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>128913035</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>128913017</v>
       </c>
       <c r="B18" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>128913014</v>
       </c>
       <c r="B22" t="n">
-        <v>88804</v>
+        <v>88807</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128913038</v>
       </c>
       <c r="B2" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128913020</v>
+        <v>128913037</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503230</v>
+        <v>503310</v>
       </c>
       <c r="R3" t="n">
-        <v>7023714</v>
+        <v>7023572</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128913037</v>
+        <v>128913020</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503310</v>
+        <v>503230</v>
       </c>
       <c r="R4" t="n">
-        <v>7023572</v>
+        <v>7023714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128913036</v>
+        <v>128913015</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>88809</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503322</v>
+        <v>503283</v>
       </c>
       <c r="R5" t="n">
-        <v>7023622</v>
+        <v>7023665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128913015</v>
+        <v>128913036</v>
       </c>
       <c r="B6" t="n">
-        <v>88807</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503283</v>
+        <v>503322</v>
       </c>
       <c r="R6" t="n">
-        <v>7023665</v>
+        <v>7023622</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1383,7 +1383,7 @@
         <v>128913013</v>
       </c>
       <c r="B9" t="n">
-        <v>88807</v>
+        <v>88809</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128913033</v>
       </c>
       <c r="B14" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>128913035</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>128913017</v>
       </c>
       <c r="B18" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>128913014</v>
       </c>
       <c r="B22" t="n">
-        <v>88807</v>
+        <v>88809</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128913015</v>
+        <v>128913036</v>
       </c>
       <c r="B5" t="n">
-        <v>88809</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503283</v>
+        <v>503322</v>
       </c>
       <c r="R5" t="n">
-        <v>7023665</v>
+        <v>7023622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128913036</v>
+        <v>128913015</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>88813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503322</v>
+        <v>503283</v>
       </c>
       <c r="R6" t="n">
-        <v>7023622</v>
+        <v>7023665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1383,7 +1383,7 @@
         <v>128913013</v>
       </c>
       <c r="B9" t="n">
-        <v>88809</v>
+        <v>88813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>128913033</v>
       </c>
       <c r="B14" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>128913014</v>
       </c>
       <c r="B22" t="n">
-        <v>88809</v>
+        <v>88813</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128913038</v>
+        <v>128913033</v>
       </c>
       <c r="B2" t="n">
-        <v>82878</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503321</v>
+        <v>503293</v>
       </c>
       <c r="R2" t="n">
-        <v>7023752</v>
+        <v>7023672</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128913037</v>
+        <v>128913038</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503310</v>
+        <v>503321</v>
       </c>
       <c r="R3" t="n">
-        <v>7023572</v>
+        <v>7023752</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128913020</v>
+        <v>128913013</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>89156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503230</v>
+        <v>503266</v>
       </c>
       <c r="R4" t="n">
-        <v>7023714</v>
+        <v>7023762</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,11 +942,6 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -959,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128913036</v>
+        <v>128913014</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>89156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503322</v>
+        <v>503302</v>
       </c>
       <c r="R5" t="n">
-        <v>7023622</v>
+        <v>7023681</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1071,7 +1066,7 @@
         <v>128913015</v>
       </c>
       <c r="B6" t="n">
-        <v>88813</v>
+        <v>89156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128913021</v>
+        <v>128913035</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503250</v>
+        <v>503242</v>
       </c>
       <c r="R7" t="n">
-        <v>7023749</v>
+        <v>7023754</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1238,11 +1233,6 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1255,73 +1245,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128913032</v>
+        <v>128913036</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503298</v>
+        <v>503322</v>
       </c>
       <c r="R8" t="n">
-        <v>7023667</v>
+        <v>7023622</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,44 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128913013</v>
+        <v>128913037</v>
       </c>
       <c r="B9" t="n">
-        <v>88813</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1415,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503266</v>
+        <v>503310</v>
       </c>
       <c r="R9" t="n">
-        <v>7023762</v>
+        <v>7023572</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128913023</v>
+        <v>128913017</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503257</v>
+        <v>503309</v>
       </c>
       <c r="R10" t="n">
-        <v>7023787</v>
+        <v>7023619</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1550,11 +1524,6 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1567,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128913030</v>
+        <v>128913018</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503276</v>
+        <v>503223</v>
       </c>
       <c r="R11" t="n">
-        <v>7023504</v>
+        <v>7023673</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,22 +1638,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128913022</v>
+        <v>128913019</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503260</v>
+        <v>503225</v>
       </c>
       <c r="R12" t="n">
-        <v>7023746</v>
+        <v>7023683</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,22 +1740,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128913028</v>
+        <v>128913020</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503344</v>
+        <v>503230</v>
       </c>
       <c r="R13" t="n">
-        <v>7023708</v>
+        <v>7023714</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,7 +1827,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1873,22 +1842,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128913033</v>
+        <v>128913021</v>
       </c>
       <c r="B14" t="n">
-        <v>91545</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503293</v>
+        <v>503250</v>
       </c>
       <c r="R14" t="n">
-        <v>7023672</v>
+        <v>7023749</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,6 +1927,11 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -1970,22 +1944,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128913035</v>
+        <v>128913022</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503242</v>
+        <v>503260</v>
       </c>
       <c r="R15" t="n">
-        <v>7023754</v>
+        <v>7023746</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2055,6 +2029,11 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2067,22 +2046,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128913024</v>
+        <v>128913023</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503250</v>
+        <v>503257</v>
       </c>
       <c r="R16" t="n">
-        <v>7023765</v>
+        <v>7023787</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,7 +2133,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2169,22 +2148,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128913019</v>
+        <v>128913024</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503225</v>
+        <v>503250</v>
       </c>
       <c r="R17" t="n">
-        <v>7023683</v>
+        <v>7023765</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,7 +2235,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2271,22 +2250,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128913017</v>
+        <v>128913025</v>
       </c>
       <c r="B18" t="n">
-        <v>83012</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2294,21 +2273,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2318,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503309</v>
+        <v>503285</v>
       </c>
       <c r="R18" t="n">
-        <v>7023619</v>
+        <v>7023527</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2356,6 +2335,11 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2368,22 +2352,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128913029</v>
+        <v>128913026</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,10 +2399,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503265</v>
+        <v>503299</v>
       </c>
       <c r="R19" t="n">
-        <v>7023517</v>
+        <v>7023511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2455,7 +2439,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2470,22 +2454,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128913026</v>
+        <v>128913027</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503299</v>
+        <v>503253</v>
       </c>
       <c r="R20" t="n">
-        <v>7023511</v>
+        <v>7023518</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,7 +2541,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2572,22 +2556,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128913025</v>
+        <v>128913028</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,10 +2603,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503285</v>
+        <v>503344</v>
       </c>
       <c r="R21" t="n">
-        <v>7023527</v>
+        <v>7023708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,7 +2643,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2674,22 +2658,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128913014</v>
+        <v>128913029</v>
       </c>
       <c r="B22" t="n">
-        <v>88813</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2697,21 +2681,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2721,10 +2705,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503302</v>
+        <v>503265</v>
       </c>
       <c r="R22" t="n">
-        <v>7023681</v>
+        <v>7023517</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2759,6 +2743,11 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2771,22 +2760,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128913018</v>
+        <v>128913030</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503223</v>
+        <v>503276</v>
       </c>
       <c r="R23" t="n">
-        <v>7023673</v>
+        <v>7023504</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2873,15 +2862,128 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128913032</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Pållbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>503298</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7023667</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39735-2021 artfynd.xlsx
+++ b/artfynd/A 39735-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913033</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913038</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913013</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913014</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913015</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913035</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913036</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913037</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913017</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913019</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913020</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913021</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913022</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2157,6 +2232,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913023</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913024</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2463,6 +2553,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913026</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2565,6 +2660,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913027</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2667,6 +2767,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913028</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2769,6 +2874,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913029</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2871,6 +2981,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913030</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2984,8 +3099,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128913032</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>